--- a/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>WHLT</t>
   </si>
@@ -656,110 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -826,8 +833,14 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,8 +907,14 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +981,14 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1013,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1083,14 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1157,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,8 +1231,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,8 +1334,10 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1328,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R17" s="3">
         <v>0</v>
@@ -1340,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="U17" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
@@ -1351,8 +1404,14 @@
       <c r="X17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1396,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3">
         <v>0</v>
@@ -1408,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="U18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V18" s="3">
         <v>0</v>
@@ -1419,8 +1478,14 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1510,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1454,17 +1521,17 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1475,14 +1542,14 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1499,22 +1566,28 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1581,8 +1654,14 @@
       <c r="X21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,8 +1728,14 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1658,17 +1743,17 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
@@ -1679,14 +1764,14 @@
         <v>0</v>
       </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
@@ -1694,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
@@ -1703,22 +1788,28 @@
         <v>-100</v>
       </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V23" s="3">
         <v>-600</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1785,8 +1876,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,8 +1950,14 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1862,17 +1965,17 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
@@ -1883,14 +1986,14 @@
         <v>0</v>
       </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
@@ -1898,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="Q26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R26" s="3">
         <v>0</v>
@@ -1907,22 +2010,28 @@
         <v>-100</v>
       </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1930,17 +2039,17 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
@@ -1951,14 +2060,14 @@
         <v>0</v>
       </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
@@ -1966,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3">
         <v>0</v>
@@ -1975,22 +2084,28 @@
         <v>-100</v>
       </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-300</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2394,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2270,17 +2409,17 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2291,14 +2430,14 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>1500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2315,22 +2454,28 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2338,17 +2483,17 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
@@ -2359,14 +2504,14 @@
         <v>0</v>
       </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
@@ -2374,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3">
         <v>0</v>
@@ -2383,22 +2528,28 @@
         <v>-100</v>
       </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-300</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,8 +2616,14 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2474,17 +2631,17 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
@@ -2495,14 +2652,14 @@
         <v>0</v>
       </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
@@ -2510,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3">
         <v>0</v>
@@ -2519,95 +2676,107 @@
         <v>-100</v>
       </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-300</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,8 +2829,10 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2676,10 +2849,10 @@
         <v>400</v>
       </c>
       <c r="H41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J41" s="3">
         <v>500</v>
@@ -2697,10 +2870,10 @@
         <v>500</v>
       </c>
       <c r="O41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q41" s="3">
         <v>600</v>
@@ -2709,10 +2882,10 @@
         <v>600</v>
       </c>
       <c r="S41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U41" s="3">
         <v>700</v>
@@ -2721,13 +2894,19 @@
         <v>700</v>
       </c>
       <c r="W41" s="3">
+        <v>700</v>
+      </c>
+      <c r="X41" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y41" s="3">
         <v>800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,8 +2973,14 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2862,8 +3047,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3121,14 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2998,8 +3195,14 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3016,10 +3219,10 @@
         <v>400</v>
       </c>
       <c r="H46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J46" s="3">
         <v>500</v>
@@ -3037,10 +3240,10 @@
         <v>500</v>
       </c>
       <c r="O46" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P46" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q46" s="3">
         <v>600</v>
@@ -3049,10 +3252,10 @@
         <v>600</v>
       </c>
       <c r="S46" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T46" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U46" s="3">
         <v>700</v>
@@ -3061,13 +3264,19 @@
         <v>700</v>
       </c>
       <c r="W46" s="3">
+        <v>700</v>
+      </c>
+      <c r="X46" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,8 +3343,14 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3202,8 +3417,14 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3474,8 +3713,14 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,8 +3787,14 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3560,10 +3811,10 @@
         <v>400</v>
       </c>
       <c r="H54" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I54" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J54" s="3">
         <v>500</v>
@@ -3581,10 +3832,10 @@
         <v>500</v>
       </c>
       <c r="O54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q54" s="3">
         <v>600</v>
@@ -3593,10 +3844,10 @@
         <v>600</v>
       </c>
       <c r="S54" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T54" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U54" s="3">
         <v>700</v>
@@ -3605,13 +3856,19 @@
         <v>700</v>
       </c>
       <c r="W54" s="3">
+        <v>700</v>
+      </c>
+      <c r="X54" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y54" s="3">
         <v>800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,8 +3921,10 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3730,8 +3991,14 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3798,8 +4065,14 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3866,8 +4139,14 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,8 +4213,14 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4002,8 +4287,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4361,14 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,8 +4583,14 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4342,8 +4657,14 @@
       <c r="X66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,10 +4905,16 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,25 +4981,31 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-8700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-8700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-8000</v>
       </c>
       <c r="I72" s="3">
         <v>-8000</v>
@@ -4667,40 +5014,40 @@
         <v>-8000</v>
       </c>
       <c r="K72" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="L72" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="M72" s="3">
         <v>-7900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-7900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-6500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-6500</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="P72" s="3">
-        <v>-6400</v>
       </c>
       <c r="Q72" s="3">
         <v>-6400</v>
       </c>
       <c r="R72" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="S72" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="T72" s="3">
         <v>-6300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-6200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-6100</v>
-      </c>
-      <c r="U72" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-5500</v>
       </c>
       <c r="W72" s="3">
         <v>-5500</v>
@@ -4708,8 +5055,14 @@
       <c r="X72" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,13 +5277,19 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E76" s="3">
         <v>400</v>
@@ -4930,10 +5301,10 @@
         <v>400</v>
       </c>
       <c r="H76" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I76" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J76" s="3">
         <v>500</v>
@@ -4951,10 +5322,10 @@
         <v>500</v>
       </c>
       <c r="O76" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P76" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q76" s="3">
         <v>600</v>
@@ -4963,10 +5334,10 @@
         <v>600</v>
       </c>
       <c r="S76" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T76" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U76" s="3">
         <v>700</v>
@@ -4975,13 +5346,19 @@
         <v>700</v>
       </c>
       <c r="W76" s="3">
+        <v>700</v>
+      </c>
+      <c r="X76" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y76" s="3">
         <v>800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,81 +5425,93 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5130,17 +5519,17 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
@@ -5151,14 +5540,14 @@
         <v>0</v>
       </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
@@ -5166,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3">
         <v>0</v>
@@ -5175,22 +5564,28 @@
         <v>-100</v>
       </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-300</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5283,8 +5680,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,8 +6050,14 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5691,8 +6124,14 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +6156,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5785,8 +6226,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6374,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5989,8 +6448,14 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,8 +6772,14 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6355,8 +6846,14 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,8 +6920,14 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6489,6 +6992,12 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WHLT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>WHLT</t>
   </si>
@@ -656,117 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,8 +843,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,8 +1362,9 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1387,17 +1414,17 @@
         <v>0</v>
       </c>
       <c r="S17" s="3">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
         <v>0</v>
       </c>
@@ -1410,8 +1437,11 @@
       <c r="Z17" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1461,17 +1491,17 @@
         <v>0</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
       <c r="U18" s="3">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
         <v>0</v>
       </c>
@@ -1484,8 +1514,11 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1521,20 +1555,20 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1548,11 +1582,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1572,11 +1606,11 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1586,16 +1620,19 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
+      <c r="E21" s="3">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>4</v>
@@ -1660,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,8 +1774,11 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1743,20 +1786,20 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
         <v>0</v>
       </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1770,11 +1813,11 @@
         <v>0</v>
       </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
@@ -1785,20 +1828,20 @@
         <v>0</v>
       </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
         <v>0</v>
       </c>
@@ -1808,8 +1851,11 @@
       <c r="Z23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1882,8 +1928,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,8 +2005,11 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1965,20 +2017,20 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>300</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
         <v>0</v>
       </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1992,11 +2044,11 @@
         <v>0</v>
       </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
@@ -2007,20 +2059,20 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
         <v>0</v>
       </c>
@@ -2030,8 +2082,11 @@
       <c r="Z26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2039,20 +2094,20 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
         <v>0</v>
       </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -2066,11 +2121,11 @@
         <v>0</v>
       </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
@@ -2081,31 +2136,34 @@
         <v>0</v>
       </c>
       <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
         <v>0</v>
       </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-300</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2409,20 +2479,20 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2436,11 +2506,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>1500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2460,11 +2530,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2474,8 +2544,11 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2483,20 +2556,20 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
         <v>0</v>
       </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -2510,11 +2583,11 @@
         <v>0</v>
       </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
@@ -2525,31 +2598,34 @@
         <v>0</v>
       </c>
       <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
         <v>0</v>
       </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-300</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,8 +2698,11 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2631,20 +2710,20 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
         <v>0</v>
       </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -2658,11 +2737,11 @@
         <v>0</v>
       </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
@@ -2673,110 +2752,116 @@
         <v>0</v>
       </c>
       <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
         <v>0</v>
       </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-300</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,13 +2917,14 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
@@ -2855,7 +2942,7 @@
         <v>400</v>
       </c>
       <c r="J41" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K41" s="3">
         <v>500</v>
@@ -2876,7 +2963,7 @@
         <v>500</v>
       </c>
       <c r="Q41" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R41" s="3">
         <v>600</v>
@@ -2888,7 +2975,7 @@
         <v>600</v>
       </c>
       <c r="U41" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V41" s="3">
         <v>700</v>
@@ -2900,13 +2987,16 @@
         <v>700</v>
       </c>
       <c r="Y41" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z41" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,8 +3069,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3201,13 +3300,16 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E46" s="3">
         <v>400</v>
@@ -3225,7 +3327,7 @@
         <v>400</v>
       </c>
       <c r="J46" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K46" s="3">
         <v>500</v>
@@ -3246,7 +3348,7 @@
         <v>500</v>
       </c>
       <c r="Q46" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R46" s="3">
         <v>600</v>
@@ -3258,7 +3360,7 @@
         <v>600</v>
       </c>
       <c r="U46" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V46" s="3">
         <v>700</v>
@@ -3270,13 +3372,16 @@
         <v>700</v>
       </c>
       <c r="Y46" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z46" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,8 +3454,11 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3423,8 +3531,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,13 +3916,16 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E54" s="3">
         <v>400</v>
@@ -3817,7 +3943,7 @@
         <v>400</v>
       </c>
       <c r="J54" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K54" s="3">
         <v>500</v>
@@ -3838,7 +3964,7 @@
         <v>500</v>
       </c>
       <c r="Q54" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R54" s="3">
         <v>600</v>
@@ -3850,7 +3976,7 @@
         <v>600</v>
       </c>
       <c r="U54" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V54" s="3">
         <v>700</v>
@@ -3862,13 +3988,16 @@
         <v>700</v>
       </c>
       <c r="Y54" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="Z54" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,8 +4053,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,8 +4205,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4145,8 +4282,11 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4293,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,8 +4744,11 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,10 +5079,13 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,28 +5158,31 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-8400</v>
+        <v>-8500</v>
       </c>
       <c r="E72" s="3">
         <v>-8400</v>
       </c>
       <c r="F72" s="3">
-        <v>-8700</v>
+        <v>-8400</v>
       </c>
       <c r="G72" s="3">
         <v>-8700</v>
       </c>
       <c r="H72" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="I72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-8000</v>
       </c>
       <c r="J72" s="3">
         <v>-8000</v>
@@ -5020,19 +5194,19 @@
         <v>-8000</v>
       </c>
       <c r="M72" s="3">
-        <v>-7900</v>
+        <v>-8000</v>
       </c>
       <c r="N72" s="3">
         <v>-7900</v>
       </c>
       <c r="O72" s="3">
-        <v>-6500</v>
+        <v>-7900</v>
       </c>
       <c r="P72" s="3">
         <v>-6500</v>
       </c>
       <c r="Q72" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="R72" s="3">
         <v>-6400</v>
@@ -5041,16 +5215,16 @@
         <v>-6400</v>
       </c>
       <c r="T72" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="U72" s="3">
         <v>-6300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-6100</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-5500</v>
       </c>
       <c r="X72" s="3">
         <v>-5500</v>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3">
         <v>-5500</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,8 +5466,11 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5292,7 +5478,7 @@
         <v>300</v>
       </c>
       <c r="E76" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F76" s="3">
         <v>400</v>
@@ -5307,7 +5493,7 @@
         <v>400</v>
       </c>
       <c r="J76" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K76" s="3">
         <v>500</v>
@@ -5328,7 +5514,7 @@
         <v>500</v>
       </c>
       <c r="Q76" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="R76" s="3">
         <v>600</v>
@@ -5340,7 +5526,7 @@
         <v>600</v>
       </c>
       <c r="U76" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V76" s="3">
         <v>700</v>
@@ -5352,13 +5538,16 @@
         <v>700</v>
       </c>
       <c r="Y76" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z76" s="3">
         <v>800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,87 +5620,93 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5519,20 +5714,20 @@
         <v>0</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
         <v>0</v>
       </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -5546,11 +5741,11 @@
         <v>0</v>
       </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
@@ -5561,31 +5756,34 @@
         <v>0</v>
       </c>
       <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
         <v>0</v>
       </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-300</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6926,8 +7175,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
